--- a/TestFiles-prod-sanity/StatementProcessing/[MLB NEW]HappyFlowChangeCheckRunDate.xlsx
+++ b/TestFiles-prod-sanity/StatementProcessing/[MLB NEW]HappyFlowChangeCheckRunDate.xlsx
@@ -76,13 +76,13 @@
     <t>Premium</t>
   </si>
   <si>
-    <t>Agent</t>
-  </si>
-  <si>
-    <t>test-DevaTest</t>
-  </si>
-  <si>
-    <t>0987654321</t>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>test-AgentX</t>
+  </si>
+  <si>
+    <t>600011</t>
   </si>
   <si>
     <t>232 E KING ST2 , ,, MALVERN, PA, 19355</t>
@@ -91,7 +91,7 @@
     <t>Integrity Health, LLC</t>
   </si>
   <si>
-    <t>IANG12370001IL001</t>
+    <t>IANG12370001IL211</t>
   </si>
   <si>
     <t>ROBERTS, PIPPIN</t>
@@ -630,7 +630,7 @@
         <v>28</v>
       </c>
       <c r="Q2" s="9">
-        <v>46024</v>
+        <v>46053</v>
       </c>
       <c r="R2" s="4" t="s">
         <v>29</v>

--- a/TestFiles-prod-sanity/StatementProcessing/[MLB NEW]HappyFlowChangeCheckRunDate.xlsx
+++ b/TestFiles-prod-sanity/StatementProcessing/[MLB NEW]HappyFlowChangeCheckRunDate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>Selling agent last name</t>
   </si>
@@ -76,13 +76,10 @@
     <t>Premium</t>
   </si>
   <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>test-AgentX</t>
-  </si>
-  <si>
-    <t>600011</t>
+    <t>ProdSL</t>
+  </si>
+  <si>
+    <t>843401317</t>
   </si>
   <si>
     <t>232 E KING ST2 , ,, MALVERN, PA, 19355</t>
@@ -91,7 +88,7 @@
     <t>Integrity Health, LLC</t>
   </si>
   <si>
-    <t>IANG12370001IL211</t>
+    <t>IANG12370001IL706</t>
   </si>
   <si>
     <t>ROBERTS, PIPPIN</t>
@@ -585,31 +582,31 @@
         <v>20</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="E2" s="8">
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="I2" s="9">
         <v>46023</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K2" s="9">
         <v>46023</v>
@@ -627,16 +624,16 @@
         <v>48.31</v>
       </c>
       <c r="P2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="9">
+        <v>46063</v>
+      </c>
+      <c r="R2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="9">
-        <v>46053</v>
-      </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="T2" s="8">
         <v>549</v>
